--- a/output/pms/Lập_trình_Python/Session 04 - Toán tử Số học, Toán tử So sánh và Toán tử Logic trong Python/Lesson 02 - Cơ chế so sánh và Biểu thức logic Boolean/Câu hỏi Quizz/Quizz_Session04_Lesson02.xlsx
+++ b/output/pms/Lập_trình_Python/Session 04 - Toán tử Số học, Toán tử So sánh và Toán tử Logic trong Python/Lesson 02 - Cơ chế so sánh và Biểu thức logic Boolean/Câu hỏi Quizz/Quizz_Session04_Lesson02.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Quizz Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quizz Questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,21 +491,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>is_discounted = True</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+          <t>is_discounted = true</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>is_discounted = true</t>
+          <t>is_discounted = "True"</t>
         </is>
       </c>
       <c r="D3" s="3" t="n"/>
@@ -525,10 +521,14 @@
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>is_discounted = "True"</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n"/>
+          <t>is_discounted = True</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Gán trực tiếp giá trị `650000` cho `is_freeship`, sau đó mới so sánh với `500000` để chuyển đổi kiểu dữ liệu thành Boolean.</t>
+          <t>Chuyển đổi cả hai biến về chuỗi ký tự, so sánh độ dài chuỗi, sau đó trả về giá trị số `1` cho biến `is_freeship`.</t>
         </is>
       </c>
       <c r="D6" s="3" t="n"/>
@@ -565,7 +565,7 @@
       <c r="B8" s="4" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Chuyển đổi cả hai biến về chuỗi ký tự, so sánh độ dài chuỗi, sau đó trả về giá trị số `1` cho biến `is_freeship`.</t>
+          <t>Gán trực tiếp giá trị `650000` cho `is_freeship`, sau đó mới so sánh với `500000` để chuyển đổi kiểu dữ liệu thành Boolean.</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>True False</t>
+          <t>False True</t>
         </is>
       </c>
       <c r="D10" s="3" t="n"/>
@@ -610,7 +610,7 @@
       <c r="B11" s="4" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>False True</t>
+          <t>False False</t>
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
@@ -620,24 +620,24 @@
       <c r="B12" s="4" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>True True</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+          <t>True False</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>False False</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n"/>
+          <t>True True</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>`stock = 0` luôn gây ra lỗi cú pháp, còn `stock == 0` là câu lệnh gán biến hợp lệ duy nhất trong ngôn ngữ Python.</t>
+          <t>`stock = 0` thực hiện phép so sánh logic trả về kiểu Boolean, còn `stock == 0` thực hiện phép tính số học cơ bản.</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
@@ -670,7 +670,7 @@
       <c r="B16" s="4" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>`stock = 0` thực hiện phép so sánh logic trả về kiểu Boolean, còn `stock == 0` thực hiện phép tính số học cơ bản.</t>
+          <t>`stock = 0` luôn gây ra lỗi cú pháp, còn `stock == 0` là câu lệnh gán biến hợp lệ duy nhất trong ngôn ngữ Python.</t>
         </is>
       </c>
       <c r="D16" s="3" t="n"/>
@@ -707,21 +707,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Kết quả là `False` vì Python so sánh khác kiểu dữ liệu giữa chuỗi (`str`) và số nguyên (`int`).</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+          <t>Chương trình báo lỗi `TypeError` vì không thể dùng toán tử `==` giữa chuỗi ký tự và số nguyên.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="4" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Kết quả là `True` vì Python tự động ép kiểu chuỗi `"18"` về số nguyên `18` trước khi so sánh.</t>
+          <t>Kết quả là `18` vì toán tử `==` sẽ trả về giá trị của biến phía sau khi hai kiểu dữ liệu không khớp nhau.</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
@@ -731,17 +727,21 @@
       <c r="B20" s="4" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Chương trình báo lỗi `TypeError` vì không thể dùng toán tử `==` giữa chuỗi ký tự và số nguyên.</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n"/>
+          <t>Kết quả là `False` vì Python so sánh khác kiểu dữ liệu giữa chuỗi (`str`) và số nguyên (`int`).</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n"/>
       <c r="B21" s="4" t="n"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Kết quả là `18` vì toán tử `==` sẽ trả về giá trị của biến phía sau khi hai kiểu dữ liệu không khớp nhau.</t>
+          <t>Kết quả là `True` vì Python tự động ép kiểu chuỗi `"18"` về số nguyên `18` trước khi so sánh.</t>
         </is>
       </c>
       <c r="D21" s="3" t="n"/>
